--- a/exports/trend_1d/SUPREMEIND_full_report.xlsx
+++ b/exports/trend_1d/SUPREMEIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>6.9</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42114</v>
+        <v>42115</v>
       </c>
       <c r="H2" t="n">
-        <v>661.9</v>
+        <v>642.1</v>
       </c>
       <c r="I2" t="n">
         <v>661.8927471857064</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K2" t="n">
-        <v>12.84</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>2.81</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>13.35</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42335</v>
+        <v>42338</v>
       </c>
       <c r="H3" t="n">
-        <v>641.54</v>
+        <v>652.5</v>
       </c>
       <c r="I3" t="n">
         <v>646.3543230963522</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K3" t="n">
-        <v>0.09</v>
+        <v>-1.62</v>
       </c>
       <c r="L3" t="n">
         <v>11.35</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>152</v>
+        <v>153</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>9</v>
+      </c>
+      <c r="U3" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.25</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42423</v>
+        <v>42424</v>
       </c>
       <c r="H4" t="n">
-        <v>672.7</v>
+        <v>665.95</v>
       </c>
       <c r="I4" t="n">
         <v>666.6374402911548</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>2.06</v>
       </c>
       <c r="L4" t="n">
         <v>20.31</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>11.75</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42431</v>
+        <v>42432</v>
       </c>
       <c r="H5" t="n">
-        <v>733.25</v>
+        <v>747.1</v>
       </c>
       <c r="I5" t="n">
         <v>743.7401586628192</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.11</v>
+        <v>-12.19</v>
       </c>
       <c r="L5" t="n">
-        <v>11.12</v>
+        <v>12.55</v>
       </c>
       <c r="M5" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="N5" t="n">
         <v>6.01</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.53</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42531</v>
+        <v>42534</v>
       </c>
       <c r="H6" t="n">
-        <v>890.1</v>
+        <v>873.1</v>
       </c>
       <c r="I6" t="n">
         <v>876.2495619677925</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K6" t="n">
-        <v>19.14</v>
+        <v>16.87</v>
       </c>
       <c r="L6" t="n">
         <v>3.03</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>11.62</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42586</v>
+        <v>42587</v>
       </c>
       <c r="H7" t="n">
-        <v>946</v>
+        <v>960.2</v>
       </c>
       <c r="I7" t="n">
         <v>947.1926365818794</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.35</v>
+        <v>-9.98</v>
       </c>
       <c r="L7" t="n">
-        <v>9.800000000000001</v>
+        <v>10.87</v>
       </c>
       <c r="M7" t="n">
         <v>1.56</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>10.24</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42625</v>
+        <v>42627</v>
       </c>
       <c r="H8" t="n">
-        <v>924.9</v>
+        <v>912.65</v>
       </c>
       <c r="I8" t="n">
         <v>915.5667256657159</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.68</v>
+        <v>-4.95</v>
       </c>
       <c r="L8" t="n">
-        <v>4.92</v>
+        <v>6.17</v>
       </c>
       <c r="M8" t="n">
         <v>1.72</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42706</v>
+        <v>42709</v>
       </c>
       <c r="H9" t="n">
-        <v>887.3</v>
+        <v>907.3</v>
       </c>
       <c r="I9" t="n">
         <v>899.9020600763788</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K9" t="n">
-        <v>2.78</v>
+        <v>0.59</v>
       </c>
       <c r="L9" t="n">
         <v>6.78</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>12.96</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42930</v>
+        <v>42933</v>
       </c>
       <c r="H10" t="n">
-        <v>1189.4</v>
+        <v>1158.05</v>
       </c>
       <c r="I10" t="n">
         <v>1164.107068550521</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K10" t="n">
-        <v>31.09</v>
+        <v>27.64</v>
       </c>
       <c r="L10" t="n">
         <v>7.41</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>153</v>
+        <v>154</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>12.18</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42970</v>
+        <v>42971</v>
       </c>
       <c r="H11" t="n">
-        <v>1124.65</v>
+        <v>1176</v>
       </c>
       <c r="I11" t="n">
         <v>1145.623496427396</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K11" t="n">
-        <v>2.88</v>
+        <v>-1.55</v>
       </c>
       <c r="L11" t="n">
-        <v>3.01</v>
+        <v>3.62</v>
       </c>
       <c r="M11" t="n">
         <v>2.01</v>
       </c>
       <c r="N11" t="n">
-        <v>4.06</v>
+        <v>4.57</v>
       </c>
       <c r="O11" t="n">
         <v>-2.64</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>13.13</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43129</v>
+        <v>43130</v>
       </c>
       <c r="H12" t="n">
-        <v>1286.6</v>
+        <v>1258.4</v>
       </c>
       <c r="I12" t="n">
         <v>1258.614985325671</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K12" t="n">
-        <v>9.4</v>
+        <v>7.01</v>
       </c>
       <c r="L12" t="n">
         <v>9.81</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>16.74</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43200</v>
+        <v>43201</v>
       </c>
       <c r="H13" t="n">
-        <v>1206.35</v>
+        <v>1303.1</v>
       </c>
       <c r="I13" t="n">
         <v>1269.917517270418</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K13" t="n">
-        <v>4.14</v>
+        <v>-3.55</v>
       </c>
       <c r="L13" t="n">
         <v>12.05</v>
@@ -1182,7 +1337,7 @@
         <v>4.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>8.02</v>
       </c>
       <c r="O13" t="n">
         <v>-2.19</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>12.4</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43257</v>
+        <v>43258</v>
       </c>
       <c r="H14" t="n">
-        <v>1260.3</v>
+        <v>1243.9</v>
       </c>
       <c r="I14" t="n">
         <v>1251.283659199765</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.28</v>
+        <v>-4.54</v>
       </c>
       <c r="L14" t="n">
         <v>7.3</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.65</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43290</v>
+        <v>43291</v>
       </c>
       <c r="H15" t="n">
-        <v>1177.4</v>
+        <v>1223.4</v>
       </c>
       <c r="I15" t="n">
         <v>1215.853241583497</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K15" t="n">
-        <v>5.35</v>
+        <v>1.65</v>
       </c>
       <c r="L15" t="n">
         <v>6.28</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>12.74</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H16" t="n">
-        <v>1130.2</v>
+        <v>1101.35</v>
       </c>
       <c r="I16" t="n">
         <v>1109.003943722076</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.62</v>
+        <v>-9.98</v>
       </c>
       <c r="L16" t="n">
-        <v>8.94</v>
+        <v>12.31</v>
       </c>
       <c r="M16" t="n">
         <v>1.47</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.74</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43446</v>
+        <v>43447</v>
       </c>
       <c r="H17" t="n">
-        <v>999.15</v>
+        <v>1050.95</v>
       </c>
       <c r="I17" t="n">
         <v>1041.500002879372</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K17" t="n">
-        <v>9.279999999999999</v>
+        <v>4.58</v>
       </c>
       <c r="L17" t="n">
         <v>3.39</v>
@@ -1410,7 +1613,7 @@
         <v>2.17</v>
       </c>
       <c r="N17" t="n">
-        <v>4.54</v>
+        <v>5.18</v>
       </c>
       <c r="O17" t="n">
         <v>-2.55</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>11.28</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43472</v>
+        <v>43473</v>
       </c>
       <c r="H18" t="n">
-        <v>1060</v>
+        <v>1039.1</v>
       </c>
       <c r="I18" t="n">
         <v>1052.878581259829</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K18" t="n">
-        <v>0.86</v>
+        <v>-1.13</v>
       </c>
       <c r="L18" t="n">
         <v>4.99</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>13.35</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43518</v>
+        <v>43521</v>
       </c>
       <c r="H19" t="n">
-        <v>1033</v>
+        <v>1072.9</v>
       </c>
       <c r="I19" t="n">
         <v>1070.728868251984</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K19" t="n">
-        <v>0.59</v>
+        <v>-3.25</v>
       </c>
       <c r="L19" t="n">
         <v>11.44</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>14.63</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43588</v>
+        <v>43591</v>
       </c>
       <c r="H20" t="n">
-        <v>1090.75</v>
+        <v>1079.25</v>
       </c>
       <c r="I20" t="n">
         <v>1081.951125358208</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K20" t="n">
-        <v>1.66</v>
+        <v>0.59</v>
       </c>
       <c r="L20" t="n">
         <v>5.3</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H21" t="n">
-        <v>1038.45</v>
+        <v>1055.35</v>
       </c>
       <c r="I21" t="n">
         <v>1049.773835838324</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K21" t="n">
-        <v>3.78</v>
+        <v>2.21</v>
       </c>
       <c r="L21" t="n">
         <v>1.17</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>10.72</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43675</v>
+        <v>43676</v>
       </c>
       <c r="H22" t="n">
-        <v>1074.85</v>
+        <v>1025.35</v>
       </c>
       <c r="I22" t="n">
         <v>1048.492420994484</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K22" t="n">
-        <v>1.85</v>
+        <v>-2.84</v>
       </c>
       <c r="L22" t="n">
-        <v>2.77</v>
+        <v>5.34</v>
       </c>
       <c r="M22" t="n">
         <v>1.71</v>
       </c>
       <c r="N22" t="n">
-        <v>2.41</v>
+        <v>4.61</v>
       </c>
       <c r="O22" t="n">
         <v>1.63</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.7</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43703</v>
+        <v>43704</v>
       </c>
       <c r="H23" t="n">
-        <v>1122.4</v>
+        <v>1142.9</v>
       </c>
       <c r="I23" t="n">
         <v>1133.682091395953</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K23" t="n">
-        <v>-9.470000000000001</v>
+        <v>-11.46</v>
       </c>
       <c r="L23" t="n">
         <v>12.64</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.77</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43769</v>
+        <v>43770</v>
       </c>
       <c r="H24" t="n">
-        <v>1164.15</v>
+        <v>1136.35</v>
       </c>
       <c r="I24" t="n">
         <v>1145.602274611648</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K24" t="n">
-        <v>1.86</v>
+        <v>-0.57</v>
       </c>
       <c r="L24" t="n">
         <v>5.68</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>13.31</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43838</v>
+        <v>43839</v>
       </c>
       <c r="H25" t="n">
-        <v>1148.1</v>
+        <v>1190.45</v>
       </c>
       <c r="I25" t="n">
         <v>1175.690393094358</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.03</v>
+        <v>-4.76</v>
       </c>
       <c r="L25" t="n">
         <v>6.92</v>
@@ -1866,7 +2165,7 @@
         <v>1.67</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>3.69</v>
       </c>
       <c r="O25" t="n">
         <v>-2.39</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43892</v>
+        <v>43893</v>
       </c>
       <c r="H26" t="n">
-        <v>1319.05</v>
+        <v>1301.75</v>
       </c>
       <c r="I26" t="n">
         <v>1304.723495011919</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K26" t="n">
-        <v>10.8</v>
+        <v>9.35</v>
       </c>
       <c r="L26" t="n">
         <v>3.82</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.19</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43942</v>
+        <v>43943</v>
       </c>
       <c r="H27" t="n">
-        <v>981.55</v>
+        <v>1038.5</v>
       </c>
       <c r="I27" t="n">
         <v>1014.161530478375</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K27" t="n">
-        <v>24.6</v>
+        <v>20.22</v>
       </c>
       <c r="L27" t="n">
         <v>1.87</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>21.18</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43964</v>
+        <v>43965</v>
       </c>
       <c r="H28" t="n">
-        <v>931.95</v>
+        <v>900.85</v>
       </c>
       <c r="I28" t="n">
         <v>930.101585621022</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" t="n">
-        <v>-10.26</v>
+        <v>-13.25</v>
       </c>
       <c r="L28" t="n">
-        <v>11.89</v>
+        <v>13.34</v>
       </c>
       <c r="M28" t="n">
         <v>3.16</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>20.06</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43984</v>
+        <v>43985</v>
       </c>
       <c r="H29" t="n">
-        <v>1045.35</v>
+        <v>1062.65</v>
       </c>
       <c r="I29" t="n">
         <v>1045.727967834172</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>-16.04</v>
+        <v>-17.96</v>
       </c>
       <c r="L29" t="n">
-        <v>17.67</v>
+        <v>19.78</v>
       </c>
       <c r="M29" t="n">
         <v>1.68</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>12.44</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44370</v>
+        <v>44371</v>
       </c>
       <c r="H30" t="n">
-        <v>2131.8</v>
+        <v>2096.65</v>
       </c>
       <c r="I30" t="n">
         <v>2106.230344946645</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K30" t="n">
-        <v>100.61</v>
+        <v>97.3</v>
       </c>
       <c r="L30" t="n">
         <v>4.73</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>266</v>
+        <v>267</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>13</v>
+      </c>
+      <c r="U30" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.81</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44435</v>
+        <v>44438</v>
       </c>
       <c r="H31" t="n">
-        <v>2090</v>
+        <v>2140.5</v>
       </c>
       <c r="I31" t="n">
         <v>2118.873187069264</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K31" t="n">
-        <v>0.32</v>
+        <v>-2.09</v>
       </c>
       <c r="L31" t="n">
         <v>5.84</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.65</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44489</v>
+        <v>44490</v>
       </c>
       <c r="H32" t="n">
-        <v>2438.65</v>
+        <v>2328.25</v>
       </c>
       <c r="I32" t="n">
         <v>2354.788569931667</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K32" t="n">
-        <v>13.93</v>
+        <v>8.77</v>
       </c>
       <c r="L32" t="n">
         <v>2.36</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>15.22</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44531</v>
+        <v>44532</v>
       </c>
       <c r="H33" t="n">
-        <v>2315.55</v>
+        <v>2397.7</v>
       </c>
       <c r="I33" t="n">
         <v>2381.333585293675</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K33" t="n">
-        <v>0.55</v>
+        <v>-2.98</v>
       </c>
       <c r="L33" t="n">
         <v>9.48</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>13.83</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44585</v>
+        <v>44586</v>
       </c>
       <c r="H34" t="n">
-        <v>2130.05</v>
+        <v>2047.85</v>
       </c>
       <c r="I34" t="n">
         <v>2102.344604599268</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K34" t="n">
-        <v>-11.16</v>
+        <v>-14.59</v>
       </c>
       <c r="L34" t="n">
-        <v>13.25</v>
+        <v>16.29</v>
       </c>
       <c r="M34" t="n">
-        <v>1.45</v>
+        <v>2.35</v>
       </c>
       <c r="N34" t="n">
         <v>4.82</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>11.24</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44655</v>
+        <v>44656</v>
       </c>
       <c r="H35" t="n">
-        <v>2038.2</v>
+        <v>2155.25</v>
       </c>
       <c r="I35" t="n">
         <v>2143.290278375788</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K35" t="n">
-        <v>0.47</v>
+        <v>-5.24</v>
       </c>
       <c r="L35" t="n">
-        <v>5.64</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M35" t="n">
         <v>4.55</v>
       </c>
       <c r="N35" t="n">
-        <v>4.55</v>
+        <v>5.74</v>
       </c>
       <c r="O35" t="n">
         <v>-3.86</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.48</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44676</v>
+        <v>44677</v>
       </c>
       <c r="H36" t="n">
-        <v>1947</v>
+        <v>1937.4</v>
       </c>
       <c r="I36" t="n">
         <v>1944.933116345171</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K36" t="n">
-        <v>-9.66</v>
+        <v>-10.11</v>
       </c>
       <c r="L36" t="n">
         <v>10.63</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44749</v>
+        <v>44750</v>
       </c>
       <c r="H37" t="n">
-        <v>1844.95</v>
+        <v>1859.8</v>
       </c>
       <c r="I37" t="n">
         <v>1856.069437292896</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K37" t="n">
-        <v>4.77</v>
+        <v>4.01</v>
       </c>
       <c r="L37" t="n">
         <v>5.81</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.92</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44847</v>
+        <v>44848</v>
       </c>
       <c r="H38" t="n">
-        <v>1975.55</v>
+        <v>1939.55</v>
       </c>
       <c r="I38" t="n">
         <v>1952.556087749876</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K38" t="n">
-        <v>6.22</v>
+        <v>4.29</v>
       </c>
       <c r="L38" t="n">
         <v>4.72</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>10.95</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44862</v>
+        <v>44865</v>
       </c>
       <c r="H39" t="n">
-        <v>2037.35</v>
+        <v>2170.3</v>
       </c>
       <c r="I39" t="n">
         <v>2148.086622445022</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.04</v>
+        <v>-11.9</v>
       </c>
       <c r="L39" t="n">
-        <v>9.300000000000001</v>
+        <v>12.91</v>
       </c>
       <c r="M39" t="n">
         <v>0.78</v>
       </c>
       <c r="N39" t="n">
-        <v>2.85</v>
+        <v>6.53</v>
       </c>
       <c r="O39" t="n">
         <v>-1.82</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>16.39</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44999</v>
+        <v>45000</v>
       </c>
       <c r="H40" t="n">
-        <v>2535.15</v>
+        <v>2488.55</v>
       </c>
       <c r="I40" t="n">
         <v>2515.184228788467</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K40" t="n">
-        <v>16.81</v>
+        <v>14.66</v>
       </c>
       <c r="L40" t="n">
         <v>10.05</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>12.07</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45040</v>
+        <v>45041</v>
       </c>
       <c r="H41" t="n">
-        <v>2685.6</v>
+        <v>2733</v>
       </c>
       <c r="I41" t="n">
         <v>2727.544628404746</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.92</v>
+        <v>-9.82</v>
       </c>
       <c r="L41" t="n">
-        <v>8.789999999999999</v>
+        <v>10.31</v>
       </c>
       <c r="M41" t="n">
         <v>0.76</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.24</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45134</v>
+        <v>45135</v>
       </c>
       <c r="H42" t="n">
-        <v>3646.5</v>
+        <v>3359.8</v>
       </c>
       <c r="I42" t="n">
         <v>3379.417467341096</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K42" t="n">
-        <v>33.42</v>
+        <v>22.93</v>
       </c>
       <c r="L42" t="n">
         <v>4.54</v>
@@ -2835,7 +3338,7 @@
         <v>1.56</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>7.86</v>
       </c>
       <c r="O42" t="n">
         <v>1.76</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>16.03</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45148</v>
+        <v>45149</v>
       </c>
       <c r="H43" t="n">
-        <v>3851.15</v>
+        <v>4071.35</v>
       </c>
       <c r="I43" t="n">
         <v>3898.287851453712</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K43" t="n">
-        <v>-14.62</v>
+        <v>-21.18</v>
       </c>
       <c r="L43" t="n">
-        <v>15.63</v>
+        <v>33.55</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1</v>
+        <v>10.02</v>
       </c>
       <c r="N43" t="n">
-        <v>5.66</v>
+        <v>5.72</v>
       </c>
       <c r="O43" t="n">
         <v>-7.86</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.13</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45189</v>
+        <v>45190</v>
       </c>
       <c r="H44" t="n">
-        <v>4169.8</v>
+        <v>4076.75</v>
       </c>
       <c r="I44" t="n">
         <v>4107.027487911252</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K44" t="n">
-        <v>2.42</v>
+        <v>0.13</v>
       </c>
       <c r="L44" t="n">
         <v>1.75</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>12.83</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45212</v>
+        <v>45215</v>
       </c>
       <c r="H45" t="n">
-        <v>4161.65</v>
+        <v>4338.95</v>
       </c>
       <c r="I45" t="n">
         <v>4307.588120937699</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.08</v>
+        <v>-6.43</v>
       </c>
       <c r="L45" t="n">
-        <v>3.89</v>
+        <v>7.81</v>
       </c>
       <c r="M45" t="n">
         <v>0.96</v>
       </c>
       <c r="N45" t="n">
-        <v>2.54</v>
+        <v>4.26</v>
       </c>
       <c r="O45" t="n">
         <v>-2.23</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>10.96</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45245</v>
+        <v>45246</v>
       </c>
       <c r="H46" t="n">
-        <v>4151.85</v>
+        <v>4070.55</v>
       </c>
       <c r="I46" t="n">
         <v>4144.127269792378</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.31</v>
+        <v>-6.19</v>
       </c>
       <c r="L46" t="n">
-        <v>5.46</v>
+        <v>6.69</v>
       </c>
       <c r="M46" t="n">
         <v>1.22</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>14.09</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45261</v>
+        <v>45264</v>
       </c>
       <c r="H47" t="n">
-        <v>4460.8</v>
+        <v>4713.2</v>
       </c>
       <c r="I47" t="n">
         <v>4533.190692097189</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K47" t="n">
-        <v>-9.59</v>
+        <v>-15.79</v>
       </c>
       <c r="L47" t="n">
-        <v>12.86</v>
+        <v>17.47</v>
       </c>
       <c r="M47" t="n">
         <v>0.5</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>14.27</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45303</v>
+        <v>45306</v>
       </c>
       <c r="H48" t="n">
-        <v>4216.75</v>
+        <v>4158.6</v>
       </c>
       <c r="I48" t="n">
         <v>4176.980690782895</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K48" t="n">
-        <v>-10.53</v>
+        <v>-11.77</v>
       </c>
       <c r="L48" t="n">
-        <v>11.21</v>
+        <v>14.25</v>
       </c>
       <c r="M48" t="n">
         <v>1.14</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45378</v>
+        <v>45379</v>
       </c>
       <c r="H49" t="n">
-        <v>4169.65</v>
+        <v>4232.2</v>
       </c>
       <c r="I49" t="n">
         <v>4177.401210894922</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.27</v>
+        <v>-1.77</v>
       </c>
       <c r="L49" t="n">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="M49" t="n">
         <v>2.09</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>14.08</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45496</v>
+        <v>45497</v>
       </c>
       <c r="H50" t="n">
-        <v>5509.1</v>
+        <v>5358.5</v>
       </c>
       <c r="I50" t="n">
         <v>5443.585409897052</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K50" t="n">
-        <v>30.17</v>
+        <v>26.61</v>
       </c>
       <c r="L50" t="n">
         <v>4.99</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>15.06</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45632</v>
+        <v>45635</v>
       </c>
       <c r="H51" t="n">
-        <v>4738.4</v>
+        <v>5012.65</v>
       </c>
       <c r="I51" t="n">
         <v>4861.500178180025</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K51" t="n">
-        <v>11.57</v>
+        <v>6.45</v>
       </c>
       <c r="L51" t="n">
         <v>6.75</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>6</v>
+      </c>
+      <c r="U51" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>12.77</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45660</v>
+        <v>45663</v>
       </c>
       <c r="H52" t="n">
-        <v>4615.15</v>
+        <v>4519.25</v>
       </c>
       <c r="I52" t="n">
         <v>4595.265388869806</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.93</v>
+        <v>-9.84</v>
       </c>
       <c r="L52" t="n">
-        <v>8.699999999999999</v>
+        <v>10.15</v>
       </c>
       <c r="M52" t="n">
         <v>1.28</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>11.93</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45769</v>
+        <v>45770</v>
       </c>
       <c r="H53" t="n">
-        <v>3522.2</v>
+        <v>3526</v>
       </c>
       <c r="I53" t="n">
         <v>3525.084671947248</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K53" t="n">
-        <v>22.06</v>
+        <v>21.98</v>
       </c>
       <c r="L53" t="n">
         <v>4.03</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.94</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="H54" t="n">
-        <v>4273.6</v>
+        <v>4196.1</v>
       </c>
       <c r="I54" t="n">
         <v>4202.173567161886</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K54" t="n">
-        <v>21.2</v>
+        <v>19</v>
       </c>
       <c r="L54" t="n">
         <v>4.95</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45883</v>
+        <v>45887</v>
       </c>
       <c r="H55" t="n">
-        <v>4297.7</v>
+        <v>4496</v>
       </c>
       <c r="I55" t="n">
         <v>4402.853861285595</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.42</v>
+        <v>-7.15</v>
       </c>
       <c r="L55" t="n">
-        <v>4.26</v>
+        <v>7.65</v>
       </c>
       <c r="M55" t="n">
         <v>1.07</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.13</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="H56" t="n">
-        <v>4348.9</v>
+        <v>4271.1</v>
       </c>
       <c r="I56" t="n">
         <v>4277.077349716797</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.27</v>
+        <v>-5</v>
       </c>
       <c r="L56" t="n">
         <v>5.44</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.83</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46022</v>
+        <v>46023</v>
       </c>
       <c r="H57" t="n">
-        <v>3353.8</v>
+        <v>3484.4</v>
       </c>
       <c r="I57" t="n">
         <v>3468.763575339287</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K57" t="n">
-        <v>21.48</v>
+        <v>18.42</v>
       </c>
       <c r="L57" t="n">
         <v>2.64</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>8.34</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H58" t="n">
-        <v>3467.3</v>
+        <v>3372.7</v>
       </c>
       <c r="I58" t="n">
         <v>3394.171508798923</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.49</v>
+        <v>-3.21</v>
       </c>
       <c r="L58" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="M58" t="n">
         <v>0.91</v>
       </c>
       <c r="N58" t="n">
-        <v>1.92</v>
+        <v>2.73</v>
       </c>
       <c r="O58" t="n">
         <v>3.89</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H59" t="n">
-        <v>3600.8</v>
+        <v>3680</v>
       </c>
       <c r="I59" t="n">
         <v>3606.928525614904</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.76</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>7.04</v>
+        <v>10.29</v>
       </c>
       <c r="M59" t="n">
-        <v>0.47</v>
+        <v>1</v>
       </c>
       <c r="N59" t="n">
         <v>4.15</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>9.07</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="H60" t="n">
-        <v>3834.4</v>
+        <v>3704.5</v>
       </c>
       <c r="I60" t="n">
         <v>3747.757768439616</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K60" t="n">
-        <v>4.2</v>
+        <v>0.67</v>
       </c>
       <c r="L60" t="n">
         <v>1.66</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>11.26</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="H61" t="n">
-        <v>3427.5</v>
+        <v>3457.8</v>
       </c>
       <c r="I61" t="n">
         <v>3452.953969278549</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K61" t="n">
-        <v>7.48</v>
+        <v>6.66</v>
       </c>
       <c r="L61" t="n">
         <v>6.39</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>5</v>
+      </c>
+      <c r="U61" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="H62" t="n">
-        <v>3510</v>
+        <v>3364.4</v>
       </c>
       <c r="I62" t="n">
         <v>3395.582215532709</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K62" t="n">
-        <v>1.51</v>
+        <v>-2.7</v>
       </c>
       <c r="L62" t="n">
         <v>4.65</v>
@@ -3975,7 +4718,7 @@
         <v>1.08</v>
       </c>
       <c r="N62" t="n">
-        <v>3.49</v>
+        <v>4.15</v>
       </c>
       <c r="O62" t="n">
         <v>0.88</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="H63" t="n">
-        <v>3344.4</v>
+        <v>3580.3</v>
       </c>
       <c r="I63" t="n">
         <v>3576.901687705746</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K63" t="n">
-        <v>0.59</v>
+        <v>-6.42</v>
       </c>
       <c r="L63" t="n">
-        <v>4</v>
+        <v>6.42</v>
       </c>
       <c r="M63" t="n">
         <v>0.14</v>
       </c>
       <c r="N63" t="n">
-        <v>1.35</v>
+        <v>7.05</v>
       </c>
       <c r="O63" t="n">
         <v>-4.15</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>11.92</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="H64" t="n">
-        <v>3390</v>
+        <v>3250</v>
       </c>
       <c r="I64" t="n">
         <v>3334.814644976531</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.32</v>
+        <v>-9.23</v>
       </c>
       <c r="L64" t="n">
-        <v>8.19</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M64" t="n">
         <v>2.24</v>
       </c>
       <c r="N64" t="n">
-        <v>2.9</v>
+        <v>4.13</v>
       </c>
       <c r="O64" t="n">
         <v>7.05</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,14 @@
       <c r="Q65" t="n">
         <v>3</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9107,7 +9894,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.7</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="6">
@@ -9117,7 +9904,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -9127,7 +9914,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8">
@@ -9137,7 +9924,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -9147,7 +9934,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.5</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="10">
@@ -9157,7 +9944,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>116.2</v>
+        <v>117.2</v>
       </c>
     </row>
     <row r="11">
@@ -9167,7 +9954,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -9177,7 +9964,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -9187,7 +9974,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25.4</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="14">
@@ -9197,7 +9984,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.36</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="15">
@@ -9207,7 +9994,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.67</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="16">
@@ -9217,7 +10004,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9399999999999999</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="17">
@@ -9227,7 +10014,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>100.61</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="18">
@@ -9237,7 +10024,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>60.3</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="19">
@@ -9247,7 +10034,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.98</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -9257,7 +10044,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.81</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="21">
@@ -9267,7 +10054,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.31</v>
+        <v>33.55</v>
       </c>
     </row>
     <row r="22">
@@ -9277,7 +10064,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -9287,7 +10074,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -9297,7 +10084,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="25">
@@ -9307,7 +10094,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.67</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="26">
@@ -9317,7 +10104,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.53</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="27">
@@ -9337,7 +10124,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
